--- a/desguace/UTI.xlsx
+++ b/desguace/UTI.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA65"/>
+  <dimension ref="A1:AB122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,6 +566,11 @@
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
+          <t>Peso(kg)</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
           <t>Categoría</t>
         </is>
       </c>
@@ -659,7 +664,8 @@
       </c>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr">
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -738,7 +744,8 @@
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr">
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -825,7 +832,8 @@
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr">
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -904,7 +912,8 @@
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr">
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -983,7 +992,8 @@
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr">
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -1078,7 +1088,8 @@
       </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr">
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -1177,7 +1188,10 @@
       <c r="Z8" t="n">
         <v>7588.4</v>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="inlineStr">
         <is>
           <t>ADITAMENTO</t>
         </is>
@@ -1272,7 +1286,8 @@
       </c>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr">
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -1371,7 +1386,10 @@
       <c r="Z10" t="n">
         <v>5.96</v>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -1470,7 +1488,10 @@
       <c r="Z11" t="n">
         <v>8.08</v>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -1565,7 +1586,8 @@
       </c>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr">
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -1660,7 +1682,8 @@
       </c>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr">
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -1755,7 +1778,8 @@
       </c>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr">
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -1846,7 +1870,10 @@
       <c r="Z15" t="n">
         <v>20</v>
       </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -1941,7 +1968,8 @@
       </c>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr">
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -2036,7 +2064,8 @@
       </c>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr">
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr">
         <is>
           <t>OPEX</t>
         </is>
@@ -2131,7 +2160,8 @@
       </c>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr">
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr">
         <is>
           <t>OPEX</t>
         </is>
@@ -2226,7 +2256,8 @@
       </c>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
-      <c r="AA19" t="inlineStr">
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -2305,7 +2336,8 @@
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
-      <c r="AA20" t="inlineStr">
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -2392,7 +2424,8 @@
       </c>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
-      <c r="AA21" t="inlineStr">
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -2471,7 +2504,8 @@
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
-      <c r="AA22" t="inlineStr">
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -2550,7 +2584,8 @@
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
-      <c r="AA23" t="inlineStr">
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -2645,7 +2680,8 @@
       </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="inlineStr">
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -2744,7 +2780,10 @@
       <c r="Z25" t="n">
         <v>5399.67</v>
       </c>
-      <c r="AA25" t="inlineStr">
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="inlineStr">
         <is>
           <t>ADITAMENTO</t>
         </is>
@@ -2843,7 +2882,10 @@
       <c r="Z26" t="n">
         <v>0</v>
       </c>
-      <c r="AA26" t="inlineStr">
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -2938,7 +2980,8 @@
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
-      <c r="AA27" t="inlineStr">
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -3033,7 +3076,8 @@
       </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
-      <c r="AA28" t="inlineStr">
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -3128,7 +3172,8 @@
       </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="inlineStr">
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -3223,7 +3268,8 @@
       </c>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
-      <c r="AA30" t="inlineStr">
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -3318,7 +3364,8 @@
       </c>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
-      <c r="AA31" t="inlineStr">
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr">
         <is>
           <t>OPEX</t>
         </is>
@@ -3413,7 +3460,8 @@
       </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
-      <c r="AA32" t="inlineStr">
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr">
         <is>
           <t>OPEX</t>
         </is>
@@ -3508,7 +3556,8 @@
       </c>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
-      <c r="AA33" t="inlineStr">
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -3587,7 +3636,8 @@
       <c r="X34" t="inlineStr"/>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr"/>
-      <c r="AA34" t="inlineStr">
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -3682,7 +3732,8 @@
       </c>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="inlineStr"/>
-      <c r="AA35" t="inlineStr">
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -3777,7 +3828,8 @@
       </c>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr"/>
-      <c r="AA36" t="inlineStr">
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -3876,7 +3928,10 @@
       <c r="Z37" t="n">
         <v>4562.6</v>
       </c>
-      <c r="AA37" t="inlineStr">
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -3971,7 +4026,8 @@
       </c>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr"/>
-      <c r="AA38" t="inlineStr">
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -4066,7 +4122,8 @@
       </c>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="inlineStr"/>
-      <c r="AA39" t="inlineStr">
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -4161,7 +4218,8 @@
       </c>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
-      <c r="AA40" t="inlineStr">
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -4240,7 +4298,8 @@
       <c r="X41" t="inlineStr"/>
       <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="inlineStr"/>
-      <c r="AA41" t="inlineStr">
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -4335,7 +4394,8 @@
       </c>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="inlineStr"/>
-      <c r="AA42" t="inlineStr">
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -4422,7 +4482,8 @@
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="inlineStr"/>
-      <c r="AA43" t="inlineStr">
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -4517,7 +4578,8 @@
       </c>
       <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="inlineStr"/>
-      <c r="AA44" t="inlineStr">
+      <c r="AA44" t="inlineStr"/>
+      <c r="AB44" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -4612,7 +4674,8 @@
       </c>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="inlineStr"/>
-      <c r="AA45" t="inlineStr">
+      <c r="AA45" t="inlineStr"/>
+      <c r="AB45" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -4707,7 +4770,8 @@
       </c>
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="inlineStr"/>
-      <c r="AA46" t="inlineStr">
+      <c r="AA46" t="inlineStr"/>
+      <c r="AB46" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -4802,7 +4866,8 @@
       </c>
       <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="inlineStr"/>
-      <c r="AA47" t="inlineStr">
+      <c r="AA47" t="inlineStr"/>
+      <c r="AB47" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -4897,7 +4962,8 @@
       </c>
       <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="inlineStr"/>
-      <c r="AA48" t="inlineStr">
+      <c r="AA48" t="inlineStr"/>
+      <c r="AB48" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -4992,7 +5058,8 @@
       </c>
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="inlineStr"/>
-      <c r="AA49" t="inlineStr">
+      <c r="AA49" t="inlineStr"/>
+      <c r="AB49" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -5071,7 +5138,8 @@
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="inlineStr"/>
-      <c r="AA50" t="inlineStr">
+      <c r="AA50" t="inlineStr"/>
+      <c r="AB50" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -5170,7 +5238,10 @@
       <c r="Z51" t="n">
         <v>6591.74</v>
       </c>
-      <c r="AA51" t="inlineStr">
+      <c r="AA51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB51" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -5269,7 +5340,10 @@
       <c r="Z52" t="n">
         <v>137.22</v>
       </c>
-      <c r="AA52" t="inlineStr">
+      <c r="AA52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB52" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -5364,7 +5438,8 @@
       </c>
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="inlineStr"/>
-      <c r="AA53" t="inlineStr">
+      <c r="AA53" t="inlineStr"/>
+      <c r="AB53" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -5459,7 +5534,8 @@
       </c>
       <c r="Y54" t="inlineStr"/>
       <c r="Z54" t="inlineStr"/>
-      <c r="AA54" t="inlineStr">
+      <c r="AA54" t="inlineStr"/>
+      <c r="AB54" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -5558,7 +5634,10 @@
       <c r="Z55" t="n">
         <v>52.40000000000001</v>
       </c>
-      <c r="AA55" t="inlineStr">
+      <c r="AA55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB55" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -5639,7 +5718,8 @@
       <c r="X56" t="inlineStr"/>
       <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="inlineStr"/>
-      <c r="AA56" t="inlineStr">
+      <c r="AA56" t="inlineStr"/>
+      <c r="AB56" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -5734,7 +5814,8 @@
       </c>
       <c r="Y57" t="inlineStr"/>
       <c r="Z57" t="inlineStr"/>
-      <c r="AA57" t="inlineStr">
+      <c r="AA57" t="inlineStr"/>
+      <c r="AB57" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -5829,7 +5910,8 @@
       </c>
       <c r="Y58" t="inlineStr"/>
       <c r="Z58" t="inlineStr"/>
-      <c r="AA58" t="inlineStr">
+      <c r="AA58" t="inlineStr"/>
+      <c r="AB58" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -5924,7 +6006,8 @@
       </c>
       <c r="Y59" t="inlineStr"/>
       <c r="Z59" t="inlineStr"/>
-      <c r="AA59" t="inlineStr">
+      <c r="AA59" t="inlineStr"/>
+      <c r="AB59" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -6019,7 +6102,8 @@
       </c>
       <c r="Y60" t="inlineStr"/>
       <c r="Z60" t="inlineStr"/>
-      <c r="AA60" t="inlineStr">
+      <c r="AA60" t="inlineStr"/>
+      <c r="AB60" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -6114,7 +6198,8 @@
       </c>
       <c r="Y61" t="inlineStr"/>
       <c r="Z61" t="inlineStr"/>
-      <c r="AA61" t="inlineStr">
+      <c r="AA61" t="inlineStr"/>
+      <c r="AB61" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -6209,7 +6294,8 @@
       </c>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="inlineStr"/>
-      <c r="AA62" t="inlineStr">
+      <c r="AA62" t="inlineStr"/>
+      <c r="AB62" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -6290,7 +6376,8 @@
       <c r="X63" t="inlineStr"/>
       <c r="Y63" t="inlineStr"/>
       <c r="Z63" t="inlineStr"/>
-      <c r="AA63" t="inlineStr">
+      <c r="AA63" t="inlineStr"/>
+      <c r="AB63" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -6385,7 +6472,8 @@
       </c>
       <c r="Y64" t="inlineStr"/>
       <c r="Z64" t="inlineStr"/>
-      <c r="AA64" t="inlineStr">
+      <c r="AA64" t="inlineStr"/>
+      <c r="AB64" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
@@ -6464,7 +6552,5404 @@
       <c r="X65" t="inlineStr"/>
       <c r="Y65" t="inlineStr"/>
       <c r="Z65" t="inlineStr"/>
-      <c r="AA65" t="inlineStr">
+      <c r="AA65" t="inlineStr"/>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>CASCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>1413</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>GP/90-225-SI</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>5016476</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>OTROS SERVICIOS INTERNOS</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>0080</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Limpieza de Carril sem 50</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>912</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>2060671352</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>MULTISERVICIOS KALEB S.A.C.</t>
+        </is>
+      </c>
+      <c r="M66" t="n">
+        <v>30019486</v>
+      </c>
+      <c r="N66" s="3" t="n">
+        <v>45984</v>
+      </c>
+      <c r="O66" s="3" t="n">
+        <v>45984</v>
+      </c>
+      <c r="P66" s="3" t="n">
+        <v>46007</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>5060097639</v>
+      </c>
+      <c r="R66" t="n">
+        <v>40</v>
+      </c>
+      <c r="S66" t="n">
+        <v>1002878971</v>
+      </c>
+      <c r="T66" s="3" t="n">
+        <v>46007</v>
+      </c>
+      <c r="U66" s="3" t="n">
+        <v>46007</v>
+      </c>
+      <c r="V66" s="3" t="n">
+        <v>46007</v>
+      </c>
+      <c r="W66" t="inlineStr"/>
+      <c r="X66" t="n">
+        <v>5105833028</v>
+      </c>
+      <c r="Y66" t="inlineStr"/>
+      <c r="Z66" t="inlineStr"/>
+      <c r="AA66" t="inlineStr"/>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>CASCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>1410</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>GP/90-225-LI</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>5016480</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Limpieza de sentina</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>801.75</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
+        <v>2056921109</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>EMPRESA DE SERVICIOS MOBYDICK S.A.C</t>
+        </is>
+      </c>
+      <c r="M67" t="n">
+        <v>30019414</v>
+      </c>
+      <c r="N67" s="3" t="n">
+        <v>46003</v>
+      </c>
+      <c r="O67" s="3" t="n">
+        <v>46003</v>
+      </c>
+      <c r="P67" s="3" t="n">
+        <v>46007</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>5060097057</v>
+      </c>
+      <c r="R67" t="n">
+        <v>30</v>
+      </c>
+      <c r="S67" t="n">
+        <v>1002853757</v>
+      </c>
+      <c r="T67" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="U67" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="V67" s="3" t="n">
+        <v>46006</v>
+      </c>
+      <c r="W67" t="inlineStr"/>
+      <c r="X67" t="n">
+        <v>5105811298</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>CASCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>1410</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>GP/90-225-LI</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>5016480</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>0080</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Limpieza de desaguadores</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>377.28</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
+        <v>2056921109</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>EMPRESA DE SERVICIOS MOBYDICK S.A.C</t>
+        </is>
+      </c>
+      <c r="M68" t="n">
+        <v>30019414</v>
+      </c>
+      <c r="N68" s="3" t="n">
+        <v>46003</v>
+      </c>
+      <c r="O68" s="3" t="n">
+        <v>46003</v>
+      </c>
+      <c r="P68" s="3" t="n">
+        <v>46007</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>5060097057</v>
+      </c>
+      <c r="R68" t="n">
+        <v>10</v>
+      </c>
+      <c r="S68" t="n">
+        <v>1002853782</v>
+      </c>
+      <c r="T68" s="3" t="n">
+        <v>46003</v>
+      </c>
+      <c r="U68" s="3" t="n">
+        <v>46003</v>
+      </c>
+      <c r="V68" s="3" t="n">
+        <v>46006</v>
+      </c>
+      <c r="W68" t="inlineStr"/>
+      <c r="X68" t="n">
+        <v>5105811298</v>
+      </c>
+      <c r="Y68" t="inlineStr"/>
+      <c r="Z68" t="inlineStr"/>
+      <c r="AA68" t="inlineStr"/>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>CASCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>1410</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>GP/90-225-LI</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>5016480</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>0090</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Limpieza fina de tanques postizos</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>110.04</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
+        <v>2056921109</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>EMPRESA DE SERVICIOS MOBYDICK S.A.C</t>
+        </is>
+      </c>
+      <c r="M69" t="n">
+        <v>30019414</v>
+      </c>
+      <c r="N69" s="3" t="n">
+        <v>46003</v>
+      </c>
+      <c r="O69" s="3" t="n">
+        <v>46003</v>
+      </c>
+      <c r="P69" s="3" t="n">
+        <v>46007</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>5060097057</v>
+      </c>
+      <c r="R69" t="n">
+        <v>20</v>
+      </c>
+      <c r="S69" t="n">
+        <v>1002853741</v>
+      </c>
+      <c r="T69" s="3" t="n">
+        <v>46003</v>
+      </c>
+      <c r="U69" s="3" t="n">
+        <v>46003</v>
+      </c>
+      <c r="V69" s="3" t="n">
+        <v>46006</v>
+      </c>
+      <c r="W69" t="inlineStr"/>
+      <c r="X69" t="n">
+        <v>5105811298</v>
+      </c>
+      <c r="Y69" t="inlineStr"/>
+      <c r="Z69" t="inlineStr"/>
+      <c r="AA69" t="inlineStr"/>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>CASCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>1410</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>GP/90-225-LI</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>5016556</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>TRASVASE</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>0070</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Trasvase de residuos oleosos de sentina</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>213.35</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
+        <v>2056921109</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>EMPRESA DE SERVICIOS MOBYDICK S.A.C</t>
+        </is>
+      </c>
+      <c r="M70" t="n">
+        <v>30019439</v>
+      </c>
+      <c r="N70" s="3" t="n">
+        <v>46003</v>
+      </c>
+      <c r="O70" s="3" t="n">
+        <v>46003</v>
+      </c>
+      <c r="P70" s="3" t="n">
+        <v>46007</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>5060097057</v>
+      </c>
+      <c r="R70" t="n">
+        <v>40</v>
+      </c>
+      <c r="S70" t="n">
+        <v>1002853752</v>
+      </c>
+      <c r="T70" s="3" t="n">
+        <v>46003</v>
+      </c>
+      <c r="U70" s="3" t="n">
+        <v>46003</v>
+      </c>
+      <c r="V70" s="3" t="n">
+        <v>46006</v>
+      </c>
+      <c r="W70" t="inlineStr"/>
+      <c r="X70" t="n">
+        <v>5105811298</v>
+      </c>
+      <c r="Y70" t="inlineStr"/>
+      <c r="Z70" t="inlineStr"/>
+      <c r="AA70" t="inlineStr"/>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>CASCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>1410</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>GP/90-225-LI</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>5016556</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>TRASVASE</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>0080</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Trasvase de agua dulce tanque br</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>213.35</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
+        <v>2056921109</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>EMPRESA DE SERVICIOS MOBYDICK S.A.C</t>
+        </is>
+      </c>
+      <c r="M71" t="n">
+        <v>30019439</v>
+      </c>
+      <c r="N71" s="3" t="n">
+        <v>46003</v>
+      </c>
+      <c r="O71" s="3" t="n">
+        <v>46003</v>
+      </c>
+      <c r="P71" s="3" t="n">
+        <v>46007</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>5060097057</v>
+      </c>
+      <c r="R71" t="n">
+        <v>50</v>
+      </c>
+      <c r="S71" t="n">
+        <v>1002853778</v>
+      </c>
+      <c r="T71" s="3" t="n">
+        <v>46003</v>
+      </c>
+      <c r="U71" s="3" t="n">
+        <v>46003</v>
+      </c>
+      <c r="V71" s="3" t="n">
+        <v>46006</v>
+      </c>
+      <c r="W71" t="inlineStr"/>
+      <c r="X71" t="n">
+        <v>5105811298</v>
+      </c>
+      <c r="Y71" t="inlineStr"/>
+      <c r="Z71" t="inlineStr"/>
+      <c r="AA71" t="inlineStr"/>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>CASCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>1410</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>GP/90-225-LI</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>5016556</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>TRASVASE</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>0090</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>2do trasvase dino hacia contenedor</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>213.35</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
+        <v>2056921109</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>EMPRESA DE SERVICIOS MOBYDICK S.A.C</t>
+        </is>
+      </c>
+      <c r="M72" t="n">
+        <v>30019439</v>
+      </c>
+      <c r="N72" s="3" t="n">
+        <v>46003</v>
+      </c>
+      <c r="O72" s="3" t="n">
+        <v>46003</v>
+      </c>
+      <c r="P72" s="3" t="n">
+        <v>46007</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>5060097057</v>
+      </c>
+      <c r="R72" t="n">
+        <v>60</v>
+      </c>
+      <c r="S72" t="n">
+        <v>1002853780</v>
+      </c>
+      <c r="T72" s="3" t="n">
+        <v>46003</v>
+      </c>
+      <c r="U72" s="3" t="n">
+        <v>46003</v>
+      </c>
+      <c r="V72" s="3" t="n">
+        <v>46006</v>
+      </c>
+      <c r="W72" t="inlineStr"/>
+      <c r="X72" t="n">
+        <v>5105811298</v>
+      </c>
+      <c r="Y72" t="inlineStr"/>
+      <c r="Z72" t="inlineStr"/>
+      <c r="AA72" t="inlineStr"/>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>CASCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>1404</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>GP/90-225-SI</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>5016476</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>OTROS SERVICIOS INTERNOS</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>0070</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Limpieza de Carril sem 49</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>228</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>2060671352</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>MULTISERVICIOS KALEB S.A.C.</t>
+        </is>
+      </c>
+      <c r="M73" t="n">
+        <v>30019486</v>
+      </c>
+      <c r="N73" s="3" t="n">
+        <v>45984</v>
+      </c>
+      <c r="O73" s="3" t="n">
+        <v>45984</v>
+      </c>
+      <c r="P73" s="3" t="n">
+        <v>46001</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>5060096716</v>
+      </c>
+      <c r="R73" t="n">
+        <v>20</v>
+      </c>
+      <c r="S73" t="n">
+        <v>1002847400</v>
+      </c>
+      <c r="T73" s="3" t="n">
+        <v>46001</v>
+      </c>
+      <c r="U73" s="3" t="n">
+        <v>46001</v>
+      </c>
+      <c r="V73" s="3" t="n">
+        <v>46001</v>
+      </c>
+      <c r="W73" t="inlineStr"/>
+      <c r="X73" t="n">
+        <v>5105833028</v>
+      </c>
+      <c r="Y73" t="inlineStr"/>
+      <c r="Z73" t="inlineStr"/>
+      <c r="AA73" t="inlineStr"/>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>CASCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>1394</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>GP/90-225-SI</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>5016476</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>OTROS SERVICIOS INTERNOS</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>0060</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Limpieza de Carril sem 47</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>1596</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>2060671352</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>MULTISERVICIOS KALEB S.A.C.</t>
+        </is>
+      </c>
+      <c r="M74" t="n">
+        <v>30019486</v>
+      </c>
+      <c r="N74" s="3" t="n">
+        <v>45984</v>
+      </c>
+      <c r="O74" s="3" t="n">
+        <v>45984</v>
+      </c>
+      <c r="P74" s="3" t="n">
+        <v>45992</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>5060096529</v>
+      </c>
+      <c r="R74" t="n">
+        <v>20</v>
+      </c>
+      <c r="S74" t="n">
+        <v>1002836630</v>
+      </c>
+      <c r="T74" s="3" t="n">
+        <v>45988</v>
+      </c>
+      <c r="U74" s="3" t="n">
+        <v>45988</v>
+      </c>
+      <c r="V74" s="3" t="n">
+        <v>45992</v>
+      </c>
+      <c r="W74" t="inlineStr"/>
+      <c r="X74" t="n">
+        <v>5105833028</v>
+      </c>
+      <c r="Y74" t="inlineStr"/>
+      <c r="Z74" t="inlineStr"/>
+      <c r="AA74" t="inlineStr"/>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>CASCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>1377</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>GP/90-225-SI</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>5016476</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>OTROS SERVICIOS INTERNOS</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>0050</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Limpieza de Carril sem 44</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>570</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>2056921109</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>EMPRESA DE SERVICIOS MOBYDICK S.A.C</t>
+        </is>
+      </c>
+      <c r="M75" t="n">
+        <v>30019486</v>
+      </c>
+      <c r="N75" s="3" t="n">
+        <v>45984</v>
+      </c>
+      <c r="O75" s="3" t="n">
+        <v>45984</v>
+      </c>
+      <c r="P75" s="3" t="n">
+        <v>45985</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>5060096161</v>
+      </c>
+      <c r="R75" t="n">
+        <v>130</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1002835344</v>
+      </c>
+      <c r="T75" s="3" t="n">
+        <v>45985</v>
+      </c>
+      <c r="U75" s="3" t="n">
+        <v>45985</v>
+      </c>
+      <c r="V75" s="3" t="n">
+        <v>45985</v>
+      </c>
+      <c r="W75" t="inlineStr"/>
+      <c r="X75" t="n">
+        <v>5105800704</v>
+      </c>
+      <c r="Y75" t="inlineStr"/>
+      <c r="Z75" t="inlineStr"/>
+      <c r="AA75" t="inlineStr"/>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>CASCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>1376</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>GP/90-225-SI</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>5016476</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>OTROS SERVICIOS INTERNOS</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>0040</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Limpieza de Carril sem 47</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>684</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>2060671352</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>MULTISERVICIOS KALEB S.A.C.</t>
+        </is>
+      </c>
+      <c r="M76" t="n">
+        <v>30019486</v>
+      </c>
+      <c r="N76" s="3" t="n">
+        <v>45984</v>
+      </c>
+      <c r="O76" s="3" t="n">
+        <v>45984</v>
+      </c>
+      <c r="P76" s="3" t="n">
+        <v>45985</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>5060096225</v>
+      </c>
+      <c r="R76" t="n">
+        <v>80</v>
+      </c>
+      <c r="S76" t="n">
+        <v>1002835388</v>
+      </c>
+      <c r="T76" s="3" t="n">
+        <v>45985</v>
+      </c>
+      <c r="U76" s="3" t="n">
+        <v>45985</v>
+      </c>
+      <c r="V76" s="3" t="n">
+        <v>45985</v>
+      </c>
+      <c r="W76" t="inlineStr"/>
+      <c r="X76" t="n">
+        <v>5105833028</v>
+      </c>
+      <c r="Y76" t="inlineStr"/>
+      <c r="Z76" t="inlineStr"/>
+      <c r="AA76" t="inlineStr"/>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>CASCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>1362</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>GP/90-225-LI</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>5016480</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>0020</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Limpieza de tanque hidráulico</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>251.53</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
+        <v>2056921109</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>EMPRESA DE SERVICIOS MOBYDICK S.A.C</t>
+        </is>
+      </c>
+      <c r="M77" t="n">
+        <v>30019414</v>
+      </c>
+      <c r="N77" s="3" t="n">
+        <v>45973</v>
+      </c>
+      <c r="O77" s="3" t="n">
+        <v>45973</v>
+      </c>
+      <c r="P77" s="3" t="n">
+        <v>45979</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>5060096161</v>
+      </c>
+      <c r="R77" t="n">
+        <v>10</v>
+      </c>
+      <c r="S77" t="n">
+        <v>1002835340</v>
+      </c>
+      <c r="T77" s="3" t="n">
+        <v>45959</v>
+      </c>
+      <c r="U77" s="3" t="n">
+        <v>45959</v>
+      </c>
+      <c r="V77" s="3" t="n">
+        <v>45978</v>
+      </c>
+      <c r="W77" t="inlineStr"/>
+      <c r="X77" t="n">
+        <v>5105800704</v>
+      </c>
+      <c r="Y77" t="inlineStr"/>
+      <c r="Z77" t="inlineStr"/>
+      <c r="AA77" t="inlineStr"/>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>CASCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>1362</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>GP/90-225-LI</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>5016480</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>0030</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Limpieza de tanque petróleo</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>1753.95</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K78" t="n">
+        <v>2056921109</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>EMPRESA DE SERVICIOS MOBYDICK S.A.C</t>
+        </is>
+      </c>
+      <c r="M78" t="n">
+        <v>30019414</v>
+      </c>
+      <c r="N78" s="3" t="n">
+        <v>45971</v>
+      </c>
+      <c r="O78" s="3" t="n">
+        <v>45972</v>
+      </c>
+      <c r="P78" s="3" t="n">
+        <v>45979</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>5060096161</v>
+      </c>
+      <c r="R78" t="n">
+        <v>20</v>
+      </c>
+      <c r="S78" t="n">
+        <v>1002835335</v>
+      </c>
+      <c r="T78" s="3" t="n">
+        <v>45959</v>
+      </c>
+      <c r="U78" s="3" t="n">
+        <v>45959</v>
+      </c>
+      <c r="V78" s="3" t="n">
+        <v>45978</v>
+      </c>
+      <c r="W78" t="inlineStr"/>
+      <c r="X78" t="n">
+        <v>5105800704</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>166</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>166</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>CASCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>1362</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>GP/90-225-LI</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>5016480</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>0040</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Limpieza de tanque agua servidas</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>220.09</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>2056921109</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>EMPRESA DE SERVICIOS MOBYDICK S.A.C</t>
+        </is>
+      </c>
+      <c r="M79" t="n">
+        <v>30019414</v>
+      </c>
+      <c r="N79" s="3" t="n">
+        <v>45971</v>
+      </c>
+      <c r="O79" s="3" t="n">
+        <v>45971</v>
+      </c>
+      <c r="P79" s="3" t="n">
+        <v>45979</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>5060096161</v>
+      </c>
+      <c r="R79" t="n">
+        <v>30</v>
+      </c>
+      <c r="S79" t="n">
+        <v>1002835351</v>
+      </c>
+      <c r="T79" s="3" t="n">
+        <v>45959</v>
+      </c>
+      <c r="U79" s="3" t="n">
+        <v>45959</v>
+      </c>
+      <c r="V79" s="3" t="n">
+        <v>45978</v>
+      </c>
+      <c r="W79" t="inlineStr"/>
+      <c r="X79" t="n">
+        <v>5105800704</v>
+      </c>
+      <c r="Y79" t="inlineStr"/>
+      <c r="Z79" t="inlineStr"/>
+      <c r="AA79" t="inlineStr"/>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>CASCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>1362</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>GP/90-225-LI</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>5016480</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>0050</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Limpieza de tanque agua dulce</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>188.65</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
+        <v>2056921109</v>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>EMPRESA DE SERVICIOS MOBYDICK S.A.C</t>
+        </is>
+      </c>
+      <c r="M80" t="n">
+        <v>30019414</v>
+      </c>
+      <c r="N80" s="3" t="n">
+        <v>45973</v>
+      </c>
+      <c r="O80" s="3" t="n">
+        <v>45973</v>
+      </c>
+      <c r="P80" s="3" t="n">
+        <v>45979</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>5060096161</v>
+      </c>
+      <c r="R80" t="n">
+        <v>40</v>
+      </c>
+      <c r="S80" t="n">
+        <v>1002835343</v>
+      </c>
+      <c r="T80" s="3" t="n">
+        <v>45959</v>
+      </c>
+      <c r="U80" s="3" t="n">
+        <v>45959</v>
+      </c>
+      <c r="V80" s="3" t="n">
+        <v>45978</v>
+      </c>
+      <c r="W80" t="inlineStr"/>
+      <c r="X80" t="n">
+        <v>5105800704</v>
+      </c>
+      <c r="Y80" t="inlineStr"/>
+      <c r="Z80" t="inlineStr"/>
+      <c r="AA80" t="inlineStr"/>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>CASCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>1362</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>GP/90-225-LI</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>5016480</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>0060</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Limpieza de túnel de propulsión</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>691.71</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K81" t="n">
+        <v>2056921109</v>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>EMPRESA DE SERVICIOS MOBYDICK S.A.C</t>
+        </is>
+      </c>
+      <c r="M81" t="n">
+        <v>30019414</v>
+      </c>
+      <c r="N81" s="3" t="n">
+        <v>45972</v>
+      </c>
+      <c r="O81" s="3" t="n">
+        <v>45973</v>
+      </c>
+      <c r="P81" s="3" t="n">
+        <v>45979</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>5060096161</v>
+      </c>
+      <c r="R81" t="n">
+        <v>50</v>
+      </c>
+      <c r="S81" t="n">
+        <v>1002835346</v>
+      </c>
+      <c r="T81" s="3" t="n">
+        <v>45959</v>
+      </c>
+      <c r="U81" s="3" t="n">
+        <v>45959</v>
+      </c>
+      <c r="V81" s="3" t="n">
+        <v>45978</v>
+      </c>
+      <c r="W81" t="inlineStr"/>
+      <c r="X81" t="n">
+        <v>5105800704</v>
+      </c>
+      <c r="Y81" t="inlineStr"/>
+      <c r="Z81" t="inlineStr"/>
+      <c r="AA81" t="inlineStr"/>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>CASCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>1362</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>GP/90-225-LI</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>5016480</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>LIMPIEZA</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>0070</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Limpieza de tanque hidrocarburos</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>251.53</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
+        <v>2056921109</v>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>EMPRESA DE SERVICIOS MOBYDICK S.A.C</t>
+        </is>
+      </c>
+      <c r="M82" t="n">
+        <v>30019414</v>
+      </c>
+      <c r="N82" s="3" t="n">
+        <v>45971</v>
+      </c>
+      <c r="O82" s="3" t="n">
+        <v>45971</v>
+      </c>
+      <c r="P82" s="3" t="n">
+        <v>45979</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>5060096161</v>
+      </c>
+      <c r="R82" t="n">
+        <v>60</v>
+      </c>
+      <c r="S82" t="n">
+        <v>1002835353</v>
+      </c>
+      <c r="T82" s="3" t="n">
+        <v>45971</v>
+      </c>
+      <c r="U82" s="3" t="n">
+        <v>45971</v>
+      </c>
+      <c r="V82" s="3" t="n">
+        <v>45978</v>
+      </c>
+      <c r="W82" t="inlineStr"/>
+      <c r="X82" t="n">
+        <v>5105800704</v>
+      </c>
+      <c r="Y82" t="inlineStr"/>
+      <c r="Z82" t="inlineStr"/>
+      <c r="AA82" t="inlineStr"/>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>CASCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>1362</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>GP/90-225-LI</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>5016556</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>TRASVASE</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Tanque Aceite Motor</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>213.35</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K83" t="n">
+        <v>2056921109</v>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>EMPRESA DE SERVICIOS MOBYDICK S.A.C</t>
+        </is>
+      </c>
+      <c r="M83" t="n">
+        <v>30019439</v>
+      </c>
+      <c r="N83" s="3" t="n">
+        <v>45973</v>
+      </c>
+      <c r="O83" s="3" t="n">
+        <v>45973</v>
+      </c>
+      <c r="P83" s="3" t="n">
+        <v>45979</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>5060096161</v>
+      </c>
+      <c r="R83" t="n">
+        <v>70</v>
+      </c>
+      <c r="S83" t="n">
+        <v>1002835376</v>
+      </c>
+      <c r="T83" s="3" t="n">
+        <v>45978</v>
+      </c>
+      <c r="U83" s="3" t="n">
+        <v>46001</v>
+      </c>
+      <c r="V83" s="3" t="n">
+        <v>45978</v>
+      </c>
+      <c r="W83" t="inlineStr"/>
+      <c r="X83" t="n">
+        <v>5105800704</v>
+      </c>
+      <c r="Y83" t="inlineStr"/>
+      <c r="Z83" t="inlineStr"/>
+      <c r="AA83" t="inlineStr"/>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>CASCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>1362</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>GP/90-225-LI</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>5016556</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>TRASVASE</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>0020</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Tanque Aceite Hidraulico</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>213.35</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>2056921109</v>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>EMPRESA DE SERVICIOS MOBYDICK S.A.C</t>
+        </is>
+      </c>
+      <c r="M84" t="n">
+        <v>30019439</v>
+      </c>
+      <c r="N84" s="3" t="n">
+        <v>45973</v>
+      </c>
+      <c r="O84" s="3" t="n">
+        <v>45973</v>
+      </c>
+      <c r="P84" s="3" t="n">
+        <v>45979</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>5060096161</v>
+      </c>
+      <c r="R84" t="n">
+        <v>80</v>
+      </c>
+      <c r="S84" t="n">
+        <v>1002835374</v>
+      </c>
+      <c r="T84" s="3" t="n">
+        <v>45978</v>
+      </c>
+      <c r="U84" s="3" t="n">
+        <v>46001</v>
+      </c>
+      <c r="V84" s="3" t="n">
+        <v>45978</v>
+      </c>
+      <c r="W84" t="inlineStr"/>
+      <c r="X84" t="n">
+        <v>5105800704</v>
+      </c>
+      <c r="Y84" t="inlineStr"/>
+      <c r="Z84" t="inlineStr"/>
+      <c r="AA84" t="inlineStr"/>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>CASCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>1362</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>GP/90-225-LI</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>5016556</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>TRASVASE</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>0030</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Tanque Aceite Hidraulico/Gobierno</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>213.35</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K85" t="n">
+        <v>2056921109</v>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>EMPRESA DE SERVICIOS MOBYDICK S.A.C</t>
+        </is>
+      </c>
+      <c r="M85" t="n">
+        <v>30019439</v>
+      </c>
+      <c r="N85" s="3" t="n">
+        <v>45973</v>
+      </c>
+      <c r="O85" s="3" t="n">
+        <v>45973</v>
+      </c>
+      <c r="P85" s="3" t="n">
+        <v>45979</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>5060096161</v>
+      </c>
+      <c r="R85" t="n">
+        <v>90</v>
+      </c>
+      <c r="S85" t="n">
+        <v>1002835375</v>
+      </c>
+      <c r="T85" s="3" t="n">
+        <v>45978</v>
+      </c>
+      <c r="U85" s="3" t="n">
+        <v>46001</v>
+      </c>
+      <c r="V85" s="3" t="n">
+        <v>45978</v>
+      </c>
+      <c r="W85" t="inlineStr"/>
+      <c r="X85" t="n">
+        <v>5105800704</v>
+      </c>
+      <c r="Y85" t="inlineStr"/>
+      <c r="Z85" t="inlineStr"/>
+      <c r="AA85" t="inlineStr"/>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>CASCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>1362</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>GP/90-225-LI</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>5016556</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>TRASVASE</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>0040</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Tanque Agua Dulce SM</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>213.35</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
+        <v>2056921109</v>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>EMPRESA DE SERVICIOS MOBYDICK S.A.C</t>
+        </is>
+      </c>
+      <c r="M86" t="n">
+        <v>30019439</v>
+      </c>
+      <c r="N86" s="3" t="n">
+        <v>45973</v>
+      </c>
+      <c r="O86" s="3" t="n">
+        <v>45973</v>
+      </c>
+      <c r="P86" s="3" t="n">
+        <v>45979</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>5060096161</v>
+      </c>
+      <c r="R86" t="n">
+        <v>100</v>
+      </c>
+      <c r="S86" t="n">
+        <v>1002835377</v>
+      </c>
+      <c r="T86" s="3" t="n">
+        <v>45978</v>
+      </c>
+      <c r="U86" s="3" t="n">
+        <v>46001</v>
+      </c>
+      <c r="V86" s="3" t="n">
+        <v>45978</v>
+      </c>
+      <c r="W86" t="inlineStr"/>
+      <c r="X86" t="n">
+        <v>5105800704</v>
+      </c>
+      <c r="Y86" t="inlineStr"/>
+      <c r="Z86" t="inlineStr"/>
+      <c r="AA86" t="inlineStr"/>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>CASCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>1362</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>GP/90-225-LI</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>5016556</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>TRASVASE</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>0050</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Residuos Oleosos Dinos/Contenedor</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>233.56</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K87" t="n">
+        <v>2056921109</v>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>EMPRESA DE SERVICIOS MOBYDICK S.A.C</t>
+        </is>
+      </c>
+      <c r="M87" t="n">
+        <v>30019439</v>
+      </c>
+      <c r="N87" s="3" t="n">
+        <v>45974</v>
+      </c>
+      <c r="O87" s="3" t="n">
+        <v>45974</v>
+      </c>
+      <c r="P87" s="3" t="n">
+        <v>45979</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>5060096161</v>
+      </c>
+      <c r="R87" t="n">
+        <v>110</v>
+      </c>
+      <c r="S87" t="n">
+        <v>1002835378</v>
+      </c>
+      <c r="T87" s="3" t="n">
+        <v>45978</v>
+      </c>
+      <c r="U87" s="3" t="n">
+        <v>46001</v>
+      </c>
+      <c r="V87" s="3" t="n">
+        <v>45978</v>
+      </c>
+      <c r="W87" t="inlineStr"/>
+      <c r="X87" t="n">
+        <v>5105800704</v>
+      </c>
+      <c r="Y87" t="inlineStr"/>
+      <c r="Z87" t="inlineStr"/>
+      <c r="AA87" t="inlineStr"/>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>CASCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>1362</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>GP/90-225-LI</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>5016556</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>TRASVASE</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>0060</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Tanques Agua Dulce Cubierta Er/Br</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>426.7</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K88" t="n">
+        <v>2056921109</v>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>EMPRESA DE SERVICIOS MOBYDICK S.A.C</t>
+        </is>
+      </c>
+      <c r="M88" t="n">
+        <v>30019439</v>
+      </c>
+      <c r="N88" s="3" t="n">
+        <v>45974</v>
+      </c>
+      <c r="O88" s="3" t="n">
+        <v>45974</v>
+      </c>
+      <c r="P88" s="3" t="n">
+        <v>45979</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>5060096161</v>
+      </c>
+      <c r="R88" t="n">
+        <v>120</v>
+      </c>
+      <c r="S88" t="n">
+        <v>1002835379</v>
+      </c>
+      <c r="T88" s="3" t="n">
+        <v>45978</v>
+      </c>
+      <c r="U88" s="3" t="n">
+        <v>46001</v>
+      </c>
+      <c r="V88" s="3" t="n">
+        <v>45978</v>
+      </c>
+      <c r="W88" t="inlineStr"/>
+      <c r="X88" t="n">
+        <v>5105800704</v>
+      </c>
+      <c r="Y88" t="inlineStr"/>
+      <c r="Z88" t="inlineStr"/>
+      <c r="AA88" t="inlineStr"/>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>CASCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>86</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>GP/90-225-SI</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>5016476</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>OTROS SERVICIOS INTERNOS</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>0120</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Servicio de Montacarga</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>5400</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K89" t="n">
+        <v>2053203078</v>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>TRANSGRUAS JHONDAVIS S.A.C.</t>
+        </is>
+      </c>
+      <c r="M89" t="n">
+        <v>30019486</v>
+      </c>
+      <c r="N89" s="3" t="n">
+        <v>45957</v>
+      </c>
+      <c r="O89" s="3" t="n">
+        <v>45957</v>
+      </c>
+      <c r="P89" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>5060100886</v>
+      </c>
+      <c r="R89" t="n">
+        <v>40</v>
+      </c>
+      <c r="S89" t="n">
+        <v>1002971155</v>
+      </c>
+      <c r="T89" s="3" t="n">
+        <v>46048</v>
+      </c>
+      <c r="U89" s="3" t="n">
+        <v>46048</v>
+      </c>
+      <c r="V89" s="3" t="n">
+        <v>46048</v>
+      </c>
+      <c r="W89" t="inlineStr"/>
+      <c r="X89" t="n">
+        <v>5105845950</v>
+      </c>
+      <c r="Y89" t="inlineStr"/>
+      <c r="Z89" t="inlineStr"/>
+      <c r="AA89" t="inlineStr"/>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>CASCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>86</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>GP/90-225-SI</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>5016476</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>OTROS SERVICIOS INTERNOS</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>0130</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Servicio de grua</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>9370</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K90" t="n">
+        <v>2053203078</v>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>TRANSGRUAS JHONDAVIS S.A.C.</t>
+        </is>
+      </c>
+      <c r="M90" t="n">
+        <v>30019486</v>
+      </c>
+      <c r="N90" s="3" t="n">
+        <v>45957</v>
+      </c>
+      <c r="O90" s="3" t="n">
+        <v>45957</v>
+      </c>
+      <c r="P90" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>5060100886</v>
+      </c>
+      <c r="R90" t="n">
+        <v>50</v>
+      </c>
+      <c r="S90" t="n">
+        <v>1002971161</v>
+      </c>
+      <c r="T90" s="3" t="n">
+        <v>46048</v>
+      </c>
+      <c r="U90" s="3" t="n">
+        <v>46048</v>
+      </c>
+      <c r="V90" s="3" t="n">
+        <v>46048</v>
+      </c>
+      <c r="W90" t="inlineStr"/>
+      <c r="X90" t="n">
+        <v>5105845950</v>
+      </c>
+      <c r="Y90" t="inlineStr"/>
+      <c r="Z90" t="inlineStr"/>
+      <c r="AA90" t="inlineStr"/>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>CASCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>86</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>GP/90-225-SI</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>5016476</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>OTROS SERVICIOS INTERNOS</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>0140</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Servicio de grua (adicional)</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
+        <v>6630</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K91" t="n">
+        <v>2053203078</v>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>TRANSGRUAS JHONDAVIS S.A.C.</t>
+        </is>
+      </c>
+      <c r="M91" t="n">
+        <v>30019486</v>
+      </c>
+      <c r="N91" s="3" t="n">
+        <v>45957</v>
+      </c>
+      <c r="O91" s="3" t="n">
+        <v>45957</v>
+      </c>
+      <c r="P91" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>5060100886</v>
+      </c>
+      <c r="R91" t="n">
+        <v>60</v>
+      </c>
+      <c r="S91" t="n">
+        <v>1002971157</v>
+      </c>
+      <c r="T91" s="3" t="n">
+        <v>46048</v>
+      </c>
+      <c r="U91" s="3" t="n">
+        <v>46048</v>
+      </c>
+      <c r="V91" s="3" t="n">
+        <v>46048</v>
+      </c>
+      <c r="W91" t="inlineStr"/>
+      <c r="X91" t="n">
+        <v>5105845950</v>
+      </c>
+      <c r="Y91" t="inlineStr"/>
+      <c r="Z91" t="inlineStr"/>
+      <c r="AA91" t="inlineStr"/>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>CASCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>80</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>GP/90-225-CA</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>5016778</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>COOLERS</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Remoción de greed/after coolers</t>
+        </is>
+      </c>
+      <c r="I92" t="n">
+        <v>725.42</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K92" t="n">
+        <v>2061013373</v>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>HERMANOS HUERTA SERVICIOS GENERALES</t>
+        </is>
+      </c>
+      <c r="M92" t="n">
+        <v>30019687</v>
+      </c>
+      <c r="N92" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="O92" s="3" t="n">
+        <v>46046</v>
+      </c>
+      <c r="P92" s="3" t="n">
+        <v>46048</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>5010255142</v>
+      </c>
+      <c r="R92" t="n">
+        <v>10</v>
+      </c>
+      <c r="S92" t="n">
+        <v>1002944338</v>
+      </c>
+      <c r="T92" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="U92" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="V92" s="3" t="n">
+        <v>46048</v>
+      </c>
+      <c r="W92" t="inlineStr"/>
+      <c r="X92" t="n">
+        <v>5105836970</v>
+      </c>
+      <c r="Y92" t="inlineStr"/>
+      <c r="Z92" t="inlineStr"/>
+      <c r="AA92" t="inlineStr"/>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>ADITAMENTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>68</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>GP/90-225-SA</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>5016553</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>DESGUACE</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>0040</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Desguace parte C</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
+        <v>4480</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K93" t="n">
+        <v>2044566087</v>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>LARCAS S.R.L.</t>
+        </is>
+      </c>
+      <c r="M93" t="n">
+        <v>30019587</v>
+      </c>
+      <c r="N93" s="3" t="n">
+        <v>46007</v>
+      </c>
+      <c r="O93" s="3" t="n">
+        <v>46007</v>
+      </c>
+      <c r="P93" s="3" t="n">
+        <v>46045</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>5010255140</v>
+      </c>
+      <c r="R93" t="n">
+        <v>10</v>
+      </c>
+      <c r="S93" t="n">
+        <v>1002944371</v>
+      </c>
+      <c r="T93" s="3" t="n">
+        <v>46045</v>
+      </c>
+      <c r="U93" s="3" t="n">
+        <v>46045</v>
+      </c>
+      <c r="V93" s="3" t="n">
+        <v>46045</v>
+      </c>
+      <c r="W93" t="inlineStr"/>
+      <c r="X93" t="n">
+        <v>5105836913</v>
+      </c>
+      <c r="Y93" t="inlineStr"/>
+      <c r="Z93" t="inlineStr"/>
+      <c r="AA93" t="inlineStr"/>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>SISTEMAS AUXILIARES</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>61</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>GP/90-225-CA</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>5016486</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>SALA DE MAQUINAS</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>0030</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Desm de accesorias de sistemas auxiliar</t>
+        </is>
+      </c>
+      <c r="I94" t="n">
+        <v>4960</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K94" t="n">
+        <v>2044522829</v>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>J MV CONTRATISTAS GENERALES EIRL</t>
+        </is>
+      </c>
+      <c r="M94" t="n">
+        <v>30019418</v>
+      </c>
+      <c r="N94" s="3" t="n">
+        <v>46006</v>
+      </c>
+      <c r="O94" s="3" t="n">
+        <v>46039</v>
+      </c>
+      <c r="P94" s="3" t="n">
+        <v>46043</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>5060099768</v>
+      </c>
+      <c r="R94" t="n">
+        <v>10</v>
+      </c>
+      <c r="S94" t="n">
+        <v>1002929504</v>
+      </c>
+      <c r="T94" s="3" t="n">
+        <v>45959</v>
+      </c>
+      <c r="U94" s="3" t="n">
+        <v>45975</v>
+      </c>
+      <c r="V94" s="3" t="n">
+        <v>46043</v>
+      </c>
+      <c r="W94" t="inlineStr"/>
+      <c r="X94" t="inlineStr"/>
+      <c r="Y94" t="n">
+        <v>261.73</v>
+      </c>
+      <c r="Z94" t="n">
+        <v>302.76</v>
+      </c>
+      <c r="AA94" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>ADITAMENTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>60</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>GP/90-225-CA</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>5016487</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>BODEGAS</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Desmontaje desaguadores y colectores</t>
+        </is>
+      </c>
+      <c r="I95" t="n">
+        <v>1860</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K95" t="n">
+        <v>2044566087</v>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>LARCAS S.R.L.</t>
+        </is>
+      </c>
+      <c r="M95" t="n">
+        <v>30019419</v>
+      </c>
+      <c r="N95" s="3" t="n">
+        <v>46006</v>
+      </c>
+      <c r="O95" s="3" t="n">
+        <v>46039</v>
+      </c>
+      <c r="P95" s="3" t="n">
+        <v>46042</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>5060099199</v>
+      </c>
+      <c r="R95" t="n">
+        <v>20</v>
+      </c>
+      <c r="S95" t="n">
+        <v>1002918070</v>
+      </c>
+      <c r="T95" s="3" t="n">
+        <v>45959</v>
+      </c>
+      <c r="U95" s="3" t="n">
+        <v>45976</v>
+      </c>
+      <c r="V95" s="3" t="n">
+        <v>46042</v>
+      </c>
+      <c r="W95" t="inlineStr"/>
+      <c r="X95" t="n">
+        <v>5105831368</v>
+      </c>
+      <c r="Y95" t="n">
+        <v>405.46</v>
+      </c>
+      <c r="Z95" t="n">
+        <v>487.46</v>
+      </c>
+      <c r="AA95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>ADITAMENTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>60</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>GP/90-225-CA</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>5016545</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>CORTE/TRATAMIENTO TERMICO</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Calderería para SP/SG</t>
+        </is>
+      </c>
+      <c r="I96" t="n">
+        <v>600</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K96" t="n">
+        <v>2044566087</v>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>LARCAS S.R.L.</t>
+        </is>
+      </c>
+      <c r="M96" t="n">
+        <v>30019471</v>
+      </c>
+      <c r="N96" s="3" t="n">
+        <v>46006</v>
+      </c>
+      <c r="O96" s="3" t="n">
+        <v>46039</v>
+      </c>
+      <c r="P96" s="3" t="n">
+        <v>46042</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>5060099199</v>
+      </c>
+      <c r="R96" t="n">
+        <v>40</v>
+      </c>
+      <c r="S96" t="n">
+        <v>1002918073</v>
+      </c>
+      <c r="T96" s="3" t="n">
+        <v>45972</v>
+      </c>
+      <c r="U96" s="3" t="n">
+        <v>45972</v>
+      </c>
+      <c r="V96" s="3" t="n">
+        <v>46042</v>
+      </c>
+      <c r="W96" t="inlineStr"/>
+      <c r="X96" t="n">
+        <v>5105831368</v>
+      </c>
+      <c r="Y96" t="n">
+        <v>128.23</v>
+      </c>
+      <c r="Z96" t="n">
+        <v>148.73</v>
+      </c>
+      <c r="AA96" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>ADITAMENTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>60</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>GP/90-225-CA</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>5016486</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>SALA DE MAQUINAS</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>0040</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Desm y evacuación</t>
+        </is>
+      </c>
+      <c r="I97" t="n">
+        <v>10750</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K97" t="n">
+        <v>2044566087</v>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>LARCAS S.R.L.</t>
+        </is>
+      </c>
+      <c r="M97" t="n">
+        <v>30019418</v>
+      </c>
+      <c r="N97" s="3" t="n">
+        <v>46006</v>
+      </c>
+      <c r="O97" s="3" t="n">
+        <v>46039</v>
+      </c>
+      <c r="P97" s="3" t="n">
+        <v>46042</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>5060099199</v>
+      </c>
+      <c r="R97" t="n">
+        <v>10</v>
+      </c>
+      <c r="S97" t="n">
+        <v>1002918071</v>
+      </c>
+      <c r="T97" s="3" t="n">
+        <v>45959</v>
+      </c>
+      <c r="U97" s="3" t="n">
+        <v>45975</v>
+      </c>
+      <c r="V97" s="3" t="n">
+        <v>46042</v>
+      </c>
+      <c r="W97" t="inlineStr"/>
+      <c r="X97" t="n">
+        <v>5105831368</v>
+      </c>
+      <c r="Y97" t="n">
+        <v>540.62</v>
+      </c>
+      <c r="Z97" t="n">
+        <v>643.6799999999999</v>
+      </c>
+      <c r="AA97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>ADITAMENTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>60</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>GP/90-225-SA</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>5016553</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>DESGUACE</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>0030</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Desguace parte B</t>
+        </is>
+      </c>
+      <c r="I98" t="n">
+        <v>16000</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K98" t="n">
+        <v>2044566087</v>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>LARCAS S.R.L.</t>
+        </is>
+      </c>
+      <c r="M98" t="n">
+        <v>30019587</v>
+      </c>
+      <c r="N98" s="3" t="n">
+        <v>46007</v>
+      </c>
+      <c r="O98" s="3" t="n">
+        <v>46007</v>
+      </c>
+      <c r="P98" s="3" t="n">
+        <v>46042</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>5010255139</v>
+      </c>
+      <c r="R98" t="n">
+        <v>10</v>
+      </c>
+      <c r="S98" t="n">
+        <v>1002944356</v>
+      </c>
+      <c r="T98" s="3" t="n">
+        <v>46042</v>
+      </c>
+      <c r="U98" s="3" t="n">
+        <v>46042</v>
+      </c>
+      <c r="V98" s="3" t="n">
+        <v>46042</v>
+      </c>
+      <c r="W98" t="inlineStr"/>
+      <c r="X98" t="n">
+        <v>5105836419</v>
+      </c>
+      <c r="Y98" t="inlineStr"/>
+      <c r="Z98" t="inlineStr"/>
+      <c r="AA98" t="inlineStr"/>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>SISTEMAS AUXILIARES</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>42</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>GP/90-225-CA</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>5016486</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>SALA DE MAQUINAS</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>0060</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Desm y evacuación tableros electricos</t>
+        </is>
+      </c>
+      <c r="I99" t="n">
+        <v>4365</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K99" t="n">
+        <v>2044566087</v>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>LARCAS S.R.L.</t>
+        </is>
+      </c>
+      <c r="M99" t="n">
+        <v>30019418</v>
+      </c>
+      <c r="N99" s="3" t="n">
+        <v>46006</v>
+      </c>
+      <c r="O99" s="3" t="n">
+        <v>46022</v>
+      </c>
+      <c r="P99" s="3" t="n">
+        <v>46038</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>5010253280</v>
+      </c>
+      <c r="R99" t="n">
+        <v>20</v>
+      </c>
+      <c r="S99" t="n">
+        <v>1002918072</v>
+      </c>
+      <c r="T99" s="3" t="n">
+        <v>46007</v>
+      </c>
+      <c r="U99" s="3" t="n">
+        <v>46007</v>
+      </c>
+      <c r="V99" s="3" t="n">
+        <v>46038</v>
+      </c>
+      <c r="W99" t="inlineStr"/>
+      <c r="X99" t="n">
+        <v>5105831350</v>
+      </c>
+      <c r="Y99" t="inlineStr"/>
+      <c r="Z99" t="inlineStr"/>
+      <c r="AA99" t="inlineStr"/>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>ADITAMENTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>42</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>GP/90-225-SA</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>5016553</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>DESGUACE</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>0020</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Desguace parte A</t>
+        </is>
+      </c>
+      <c r="I100" t="n">
+        <v>16000</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K100" t="n">
+        <v>2044566087</v>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>LARCAS S.R.L.</t>
+        </is>
+      </c>
+      <c r="M100" t="n">
+        <v>30019587</v>
+      </c>
+      <c r="N100" s="3" t="n">
+        <v>46007</v>
+      </c>
+      <c r="O100" s="3" t="n">
+        <v>46007</v>
+      </c>
+      <c r="P100" s="3" t="n">
+        <v>46038</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>5010253280</v>
+      </c>
+      <c r="R100" t="n">
+        <v>10</v>
+      </c>
+      <c r="S100" t="n">
+        <v>1002918063</v>
+      </c>
+      <c r="T100" s="3" t="n">
+        <v>46038</v>
+      </c>
+      <c r="U100" s="3" t="n">
+        <v>46038</v>
+      </c>
+      <c r="V100" s="3" t="n">
+        <v>46038</v>
+      </c>
+      <c r="W100" t="inlineStr"/>
+      <c r="X100" t="n">
+        <v>5105831350</v>
+      </c>
+      <c r="Y100" t="inlineStr"/>
+      <c r="Z100" t="inlineStr"/>
+      <c r="AA100" t="inlineStr"/>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>SISTEMAS AUXILIARES</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>21</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>GP/90-225-SI</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>5016476</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>OTROS SERVICIOS INTERNOS</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>0110</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Limpieza de Carril sem 52-1</t>
+        </is>
+      </c>
+      <c r="I101" t="n">
+        <v>798</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K101" t="n">
+        <v>2056921109</v>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>EMPRESA DE SERVICIOS MOBYDICK S.A.C</t>
+        </is>
+      </c>
+      <c r="M101" t="n">
+        <v>30019486</v>
+      </c>
+      <c r="N101" s="3" t="n">
+        <v>45984</v>
+      </c>
+      <c r="O101" s="3" t="n">
+        <v>45984</v>
+      </c>
+      <c r="P101" s="3" t="n">
+        <v>46029</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>5060098410</v>
+      </c>
+      <c r="R101" t="n">
+        <v>40</v>
+      </c>
+      <c r="S101" t="n">
+        <v>1002891024</v>
+      </c>
+      <c r="T101" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="U101" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="V101" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="W101" t="inlineStr"/>
+      <c r="X101" t="n">
+        <v>5105820121</v>
+      </c>
+      <c r="Y101" t="inlineStr"/>
+      <c r="Z101" t="inlineStr"/>
+      <c r="AA101" t="inlineStr"/>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>CASCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>16</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>GP/90-225-LI</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>5016770</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>CARPINTERIA</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Desmontaje de enjaretado</t>
+        </is>
+      </c>
+      <c r="I102" t="n">
+        <v>2114.52</v>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K102" t="n">
+        <v>2060671352</v>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>MULTISERVICIOS KALEB S.A.C.</t>
+        </is>
+      </c>
+      <c r="M102" t="n">
+        <v>30019685</v>
+      </c>
+      <c r="N102" s="3" t="n">
+        <v>46011</v>
+      </c>
+      <c r="O102" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="P102" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>5010255138</v>
+      </c>
+      <c r="R102" t="n">
+        <v>10</v>
+      </c>
+      <c r="S102" t="n">
+        <v>1002944379</v>
+      </c>
+      <c r="T102" s="3" t="n">
+        <v>46024</v>
+      </c>
+      <c r="U102" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="V102" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="W102" t="inlineStr"/>
+      <c r="X102" t="inlineStr"/>
+      <c r="Y102" t="inlineStr"/>
+      <c r="Z102" t="inlineStr"/>
+      <c r="AA102" t="inlineStr"/>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>CASCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>13</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>GP/90-225-PG</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>5016739</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>DESMONTAJE</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Desmontaje de SP 04</t>
+        </is>
+      </c>
+      <c r="I103" t="n">
+        <v>2970</v>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K103" t="n">
+        <v>2044543222</v>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>MULTISERVICIOS Z &amp; R E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="M103" t="n">
+        <v>30019658</v>
+      </c>
+      <c r="N103" s="3" t="n">
+        <v>46020</v>
+      </c>
+      <c r="O103" s="3" t="n">
+        <v>46020</v>
+      </c>
+      <c r="P103" s="3" t="n">
+        <v>46027</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>5060098408</v>
+      </c>
+      <c r="R103" t="n">
+        <v>10</v>
+      </c>
+      <c r="S103" t="n">
+        <v>1002891027</v>
+      </c>
+      <c r="T103" s="3" t="n">
+        <v>46017</v>
+      </c>
+      <c r="U103" s="3" t="n">
+        <v>46027</v>
+      </c>
+      <c r="V103" s="3" t="n">
+        <v>46027</v>
+      </c>
+      <c r="W103" t="inlineStr"/>
+      <c r="X103" t="n">
+        <v>5105831983</v>
+      </c>
+      <c r="Y103" t="inlineStr"/>
+      <c r="Z103" t="inlineStr"/>
+      <c r="AA103" t="inlineStr"/>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>PROPULSION Y GOBIERNO</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>13</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>GP/90-225-PG</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>5016739</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>DESMONTAJE</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>0020</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Desmontaje SG</t>
+        </is>
+      </c>
+      <c r="I104" t="n">
+        <v>1128</v>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K104" t="n">
+        <v>2044543222</v>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>MULTISERVICIOS Z &amp; R E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="M104" t="n">
+        <v>30019658</v>
+      </c>
+      <c r="N104" s="3" t="n">
+        <v>46020</v>
+      </c>
+      <c r="O104" s="3" t="n">
+        <v>46020</v>
+      </c>
+      <c r="P104" s="3" t="n">
+        <v>46027</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>5060098408</v>
+      </c>
+      <c r="R104" t="n">
+        <v>20</v>
+      </c>
+      <c r="S104" t="n">
+        <v>1002891028</v>
+      </c>
+      <c r="T104" s="3" t="n">
+        <v>46017</v>
+      </c>
+      <c r="U104" s="3" t="n">
+        <v>46027</v>
+      </c>
+      <c r="V104" s="3" t="n">
+        <v>46027</v>
+      </c>
+      <c r="W104" t="inlineStr"/>
+      <c r="X104" t="n">
+        <v>5105831983</v>
+      </c>
+      <c r="Y104" t="inlineStr"/>
+      <c r="Z104" t="inlineStr"/>
+      <c r="AA104" t="inlineStr"/>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>PROPULSION Y GOBIERNO</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>13</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>GP/90-225-PG</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>5016739</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>DESMONTAJE</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>0030</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Desmontaje de motor/caja/grupos</t>
+        </is>
+      </c>
+      <c r="I105" t="n">
+        <v>2090</v>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K105" t="n">
+        <v>2044543222</v>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>MULTISERVICIOS Z &amp; R E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="M105" t="n">
+        <v>30019658</v>
+      </c>
+      <c r="N105" s="3" t="n">
+        <v>46006</v>
+      </c>
+      <c r="O105" s="3" t="n">
+        <v>46018</v>
+      </c>
+      <c r="P105" s="3" t="n">
+        <v>46027</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>5060098408</v>
+      </c>
+      <c r="R105" t="n">
+        <v>30</v>
+      </c>
+      <c r="S105" t="n">
+        <v>1002891029</v>
+      </c>
+      <c r="T105" s="3" t="n">
+        <v>46017</v>
+      </c>
+      <c r="U105" s="3" t="n">
+        <v>46027</v>
+      </c>
+      <c r="V105" s="3" t="n">
+        <v>46027</v>
+      </c>
+      <c r="W105" t="inlineStr"/>
+      <c r="X105" t="n">
+        <v>5105831983</v>
+      </c>
+      <c r="Y105" t="inlineStr"/>
+      <c r="Z105" t="inlineStr"/>
+      <c r="AA105" t="inlineStr"/>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>PROPULSION Y GOBIERNO</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>7</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>GP/90-225-SI</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>5016476</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>OTROS SERVICIOS INTERNOS</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>0100</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Limpieza de Carril sem 51</t>
+        </is>
+      </c>
+      <c r="I106" t="n">
+        <v>513</v>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K106" t="n">
+        <v>2056921109</v>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>EMPRESA DE SERVICIOS MOBYDICK S.A.C</t>
+        </is>
+      </c>
+      <c r="M106" t="n">
+        <v>30019486</v>
+      </c>
+      <c r="N106" s="3" t="n">
+        <v>45984</v>
+      </c>
+      <c r="O106" s="3" t="n">
+        <v>45984</v>
+      </c>
+      <c r="P106" s="3" t="n">
+        <v>46027</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>5060098410</v>
+      </c>
+      <c r="R106" t="n">
+        <v>30</v>
+      </c>
+      <c r="S106" t="n">
+        <v>1002891021</v>
+      </c>
+      <c r="T106" s="3" t="n">
+        <v>46024</v>
+      </c>
+      <c r="U106" s="3" t="n">
+        <v>46024</v>
+      </c>
+      <c r="V106" s="3" t="n">
+        <v>46024</v>
+      </c>
+      <c r="W106" t="inlineStr"/>
+      <c r="X106" t="n">
+        <v>5105820121</v>
+      </c>
+      <c r="Y106" t="inlineStr"/>
+      <c r="Z106" t="inlineStr"/>
+      <c r="AA106" t="inlineStr"/>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>CASCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>6</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>GP/90-225-CA</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>5016488</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>LASTRE</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Remoción/Evacuación Lastre</t>
+        </is>
+      </c>
+      <c r="I107" t="n">
+        <v>9224.290000000001</v>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K107" t="n">
+        <v>2060025375</v>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>SERVICIOS GENERALES JORMER S.A.C.</t>
+        </is>
+      </c>
+      <c r="M107" t="n">
+        <v>30019430</v>
+      </c>
+      <c r="N107" s="3" t="n">
+        <v>46008</v>
+      </c>
+      <c r="O107" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="P107" s="3" t="n">
+        <v>46024</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>5010251658</v>
+      </c>
+      <c r="R107" t="n">
+        <v>10</v>
+      </c>
+      <c r="S107" t="n">
+        <v>1002894084</v>
+      </c>
+      <c r="T107" s="3" t="n">
+        <v>45959</v>
+      </c>
+      <c r="U107" s="3" t="n">
+        <v>46024</v>
+      </c>
+      <c r="V107" s="3" t="n">
+        <v>46024</v>
+      </c>
+      <c r="W107" t="inlineStr"/>
+      <c r="X107" t="n">
+        <v>5105823192</v>
+      </c>
+      <c r="Y107" t="inlineStr"/>
+      <c r="Z107" t="inlineStr"/>
+      <c r="AA107" t="inlineStr"/>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>ADITAMENTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>2</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>GP/90-225-SI</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>5016476</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>OTROS SERVICIOS INTERNOS</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>0090</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Servicio de Montacarga</t>
+        </is>
+      </c>
+      <c r="I108" t="n">
+        <v>900</v>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K108" t="n">
+        <v>2053203078</v>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>TRANSGRUAS JHONDAVIS S.A.C.</t>
+        </is>
+      </c>
+      <c r="M108" t="n">
+        <v>30019486</v>
+      </c>
+      <c r="N108" s="3" t="n">
+        <v>45957</v>
+      </c>
+      <c r="O108" s="3" t="n">
+        <v>45957</v>
+      </c>
+      <c r="P108" s="3" t="n">
+        <v>46024</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>5010251654</v>
+      </c>
+      <c r="R108" t="n">
+        <v>10</v>
+      </c>
+      <c r="S108" t="n">
+        <v>1002894085</v>
+      </c>
+      <c r="T108" s="3" t="n">
+        <v>46020</v>
+      </c>
+      <c r="U108" s="3" t="n">
+        <v>46020</v>
+      </c>
+      <c r="V108" s="3" t="n">
+        <v>46020</v>
+      </c>
+      <c r="W108" t="inlineStr"/>
+      <c r="X108" t="n">
+        <v>5105823769</v>
+      </c>
+      <c r="Y108" t="inlineStr"/>
+      <c r="Z108" t="inlineStr"/>
+      <c r="AA108" t="inlineStr"/>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>CASCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>0</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>GP/90-225-SI</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>5016475</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>TRABAJOS INICIALES</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>VARADA / DESVARADA</t>
+        </is>
+      </c>
+      <c r="I109" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" s="3" t="n">
+        <v>45957</v>
+      </c>
+      <c r="O109" s="3" t="n">
+        <v>45957</v>
+      </c>
+      <c r="P109" t="inlineStr"/>
+      <c r="Q109" t="inlineStr"/>
+      <c r="R109" t="n">
+        <v>0</v>
+      </c>
+      <c r="S109" t="inlineStr"/>
+      <c r="T109" s="3" t="n">
+        <v>45957</v>
+      </c>
+      <c r="U109" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="V109" t="inlineStr"/>
+      <c r="W109" t="inlineStr"/>
+      <c r="X109" t="inlineStr"/>
+      <c r="Y109" t="inlineStr"/>
+      <c r="Z109" t="inlineStr"/>
+      <c r="AA109" t="inlineStr"/>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>CASCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>0</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>GP/90-225-SI</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>5016475</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>TRABAJOS INICIALES</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>0020</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>ESTADIA DE LA EMBARCACION</t>
+        </is>
+      </c>
+      <c r="I110" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" s="3" t="n">
+        <v>45957</v>
+      </c>
+      <c r="O110" s="3" t="n">
+        <v>45957</v>
+      </c>
+      <c r="P110" t="inlineStr"/>
+      <c r="Q110" t="inlineStr"/>
+      <c r="R110" t="n">
+        <v>0</v>
+      </c>
+      <c r="S110" t="inlineStr"/>
+      <c r="T110" s="3" t="n">
+        <v>45957</v>
+      </c>
+      <c r="U110" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="V110" t="inlineStr"/>
+      <c r="W110" t="inlineStr"/>
+      <c r="X110" t="inlineStr"/>
+      <c r="Y110" t="inlineStr"/>
+      <c r="Z110" t="inlineStr"/>
+      <c r="AA110" t="inlineStr"/>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>CASCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>0</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>GP/90-225-SI</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>5016475</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>TRABAJOS INICIALES</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>0030</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>EXPEDIENTE</t>
+        </is>
+      </c>
+      <c r="I111" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" s="3" t="n">
+        <v>45980</v>
+      </c>
+      <c r="O111" s="3" t="n">
+        <v>45980</v>
+      </c>
+      <c r="P111" t="inlineStr"/>
+      <c r="Q111" t="inlineStr"/>
+      <c r="R111" t="n">
+        <v>0</v>
+      </c>
+      <c r="S111" t="inlineStr"/>
+      <c r="T111" s="3" t="n">
+        <v>45980</v>
+      </c>
+      <c r="U111" s="3" t="n">
+        <v>45980</v>
+      </c>
+      <c r="V111" t="inlineStr"/>
+      <c r="W111" t="inlineStr"/>
+      <c r="X111" t="inlineStr"/>
+      <c r="Y111" t="inlineStr"/>
+      <c r="Z111" t="inlineStr"/>
+      <c r="AA111" t="inlineStr"/>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>CASCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>0</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>GP/90-225-CA</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>5016479</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>PUENTE DE MANDO</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Desm equipos electrónicos y eléctricos</t>
+        </is>
+      </c>
+      <c r="I112" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="n">
+        <v>30019413</v>
+      </c>
+      <c r="N112" s="3" t="n">
+        <v>45957</v>
+      </c>
+      <c r="O112" s="3" t="n">
+        <v>45957</v>
+      </c>
+      <c r="P112" t="inlineStr"/>
+      <c r="Q112" t="inlineStr"/>
+      <c r="R112" t="n">
+        <v>0</v>
+      </c>
+      <c r="S112" t="inlineStr"/>
+      <c r="T112" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="U112" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="V112" t="inlineStr"/>
+      <c r="W112" t="inlineStr"/>
+      <c r="X112" t="inlineStr"/>
+      <c r="Y112" t="inlineStr"/>
+      <c r="Z112" t="inlineStr"/>
+      <c r="AA112" t="inlineStr"/>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>ADITAMENTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>0</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>GP/90-225-CA</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>5016479</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>PUENTE DE MANDO</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>0020</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Desm equipos hidráulicos</t>
+        </is>
+      </c>
+      <c r="I113" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="n">
+        <v>30019413</v>
+      </c>
+      <c r="N113" s="3" t="n">
+        <v>45957</v>
+      </c>
+      <c r="O113" s="3" t="n">
+        <v>45957</v>
+      </c>
+      <c r="P113" t="inlineStr"/>
+      <c r="Q113" t="inlineStr"/>
+      <c r="R113" t="n">
+        <v>0</v>
+      </c>
+      <c r="S113" t="inlineStr"/>
+      <c r="T113" s="3" t="n">
+        <v>45959</v>
+      </c>
+      <c r="U113" s="3" t="n">
+        <v>45959</v>
+      </c>
+      <c r="V113" t="inlineStr"/>
+      <c r="W113" t="inlineStr"/>
+      <c r="X113" t="inlineStr"/>
+      <c r="Y113" t="inlineStr"/>
+      <c r="Z113" t="inlineStr"/>
+      <c r="AA113" t="inlineStr"/>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>ADITAMENTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>0</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>GP/90-225-CA</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>5016479</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>PUENTE DE MANDO</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>0030</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Desm puente de mando y habitabilidad</t>
+        </is>
+      </c>
+      <c r="I114" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="n">
+        <v>30019413</v>
+      </c>
+      <c r="N114" s="3" t="n">
+        <v>45957</v>
+      </c>
+      <c r="O114" s="3" t="n">
+        <v>45957</v>
+      </c>
+      <c r="P114" t="inlineStr"/>
+      <c r="Q114" t="inlineStr"/>
+      <c r="R114" t="n">
+        <v>0</v>
+      </c>
+      <c r="S114" t="inlineStr"/>
+      <c r="T114" s="3" t="n">
+        <v>45959</v>
+      </c>
+      <c r="U114" s="3" t="n">
+        <v>45959</v>
+      </c>
+      <c r="V114" t="inlineStr"/>
+      <c r="W114" t="inlineStr"/>
+      <c r="X114" t="inlineStr"/>
+      <c r="Y114" t="inlineStr"/>
+      <c r="Z114" t="inlineStr"/>
+      <c r="AA114" t="inlineStr"/>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>ADITAMENTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>0</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>GP/90-225-CA</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>5016479</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>PUENTE DE MANDO</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>0040</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Desm tanque agua dulce</t>
+        </is>
+      </c>
+      <c r="I115" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="n">
+        <v>30019413</v>
+      </c>
+      <c r="N115" s="3" t="n">
+        <v>45957</v>
+      </c>
+      <c r="O115" s="3" t="n">
+        <v>45957</v>
+      </c>
+      <c r="P115" t="inlineStr"/>
+      <c r="Q115" t="inlineStr"/>
+      <c r="R115" t="n">
+        <v>0</v>
+      </c>
+      <c r="S115" t="inlineStr"/>
+      <c r="T115" s="3" t="n">
+        <v>45959</v>
+      </c>
+      <c r="U115" s="3" t="n">
+        <v>45959</v>
+      </c>
+      <c r="V115" t="inlineStr"/>
+      <c r="W115" t="inlineStr"/>
+      <c r="X115" t="inlineStr"/>
+      <c r="Y115" t="inlineStr"/>
+      <c r="Z115" t="inlineStr"/>
+      <c r="AA115" t="inlineStr"/>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>ADITAMENTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>0</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>GP/90-225-CA</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>5016485</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>CASETA</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Desm equipos en caseta</t>
+        </is>
+      </c>
+      <c r="I116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="n">
+        <v>30019417</v>
+      </c>
+      <c r="N116" s="3" t="n">
+        <v>45957</v>
+      </c>
+      <c r="O116" s="3" t="n">
+        <v>45957</v>
+      </c>
+      <c r="P116" t="inlineStr"/>
+      <c r="Q116" t="inlineStr"/>
+      <c r="R116" t="n">
+        <v>0</v>
+      </c>
+      <c r="S116" t="inlineStr"/>
+      <c r="T116" s="3" t="n">
+        <v>45959</v>
+      </c>
+      <c r="U116" s="3" t="n">
+        <v>46024</v>
+      </c>
+      <c r="V116" t="inlineStr"/>
+      <c r="W116" t="inlineStr"/>
+      <c r="X116" t="inlineStr"/>
+      <c r="Y116" t="inlineStr"/>
+      <c r="Z116" t="inlineStr"/>
+      <c r="AA116" t="inlineStr"/>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>ADITAMENTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>0</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>GP/90-225-CA</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>5016486</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>SALA DE MAQUINAS</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Desm y evacuación de motor/caja</t>
+        </is>
+      </c>
+      <c r="I117" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="n">
+        <v>30019418</v>
+      </c>
+      <c r="N117" s="3" t="n">
+        <v>45957</v>
+      </c>
+      <c r="O117" s="3" t="n">
+        <v>45957</v>
+      </c>
+      <c r="P117" t="inlineStr"/>
+      <c r="Q117" t="inlineStr"/>
+      <c r="R117" t="n">
+        <v>0</v>
+      </c>
+      <c r="S117" t="inlineStr"/>
+      <c r="T117" s="3" t="n">
+        <v>45959</v>
+      </c>
+      <c r="U117" s="3" t="n">
+        <v>45975</v>
+      </c>
+      <c r="V117" t="inlineStr"/>
+      <c r="W117" t="inlineStr"/>
+      <c r="X117" t="inlineStr"/>
+      <c r="Y117" t="inlineStr"/>
+      <c r="Z117" t="inlineStr"/>
+      <c r="AA117" t="inlineStr"/>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>ADITAMENTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>0</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>GP/90-225-CA</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>5016486</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>SALA DE MAQUINAS</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>0020</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Remc de aislamiento de escape</t>
+        </is>
+      </c>
+      <c r="I118" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="n">
+        <v>30019418</v>
+      </c>
+      <c r="N118" s="3" t="n">
+        <v>45957</v>
+      </c>
+      <c r="O118" s="3" t="n">
+        <v>45957</v>
+      </c>
+      <c r="P118" t="inlineStr"/>
+      <c r="Q118" t="inlineStr"/>
+      <c r="R118" t="n">
+        <v>0</v>
+      </c>
+      <c r="S118" t="inlineStr"/>
+      <c r="T118" s="3" t="n">
+        <v>45959</v>
+      </c>
+      <c r="U118" s="3" t="n">
+        <v>45975</v>
+      </c>
+      <c r="V118" t="inlineStr"/>
+      <c r="W118" t="inlineStr"/>
+      <c r="X118" t="inlineStr"/>
+      <c r="Y118" t="inlineStr"/>
+      <c r="Z118" t="inlineStr"/>
+      <c r="AA118" t="inlineStr"/>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>ADITAMENTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>0</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>GP/90-225-CA</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>5016486</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>SALA DE MAQUINAS</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>0050</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Desm y evacuación de bombas</t>
+        </is>
+      </c>
+      <c r="I119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="n">
+        <v>30019418</v>
+      </c>
+      <c r="N119" s="3" t="n">
+        <v>45957</v>
+      </c>
+      <c r="O119" s="3" t="n">
+        <v>45957</v>
+      </c>
+      <c r="P119" t="inlineStr"/>
+      <c r="Q119" t="inlineStr"/>
+      <c r="R119" t="n">
+        <v>0</v>
+      </c>
+      <c r="S119" t="inlineStr"/>
+      <c r="T119" s="3" t="n">
+        <v>45959</v>
+      </c>
+      <c r="U119" s="3" t="n">
+        <v>45975</v>
+      </c>
+      <c r="V119" t="inlineStr"/>
+      <c r="W119" t="inlineStr"/>
+      <c r="X119" t="inlineStr"/>
+      <c r="Y119" t="inlineStr"/>
+      <c r="Z119" t="inlineStr"/>
+      <c r="AA119" t="inlineStr"/>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>ADITAMENTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>0</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>GP/90-225-SA</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>5016553</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>DESGUACE</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Desguace estructura</t>
+        </is>
+      </c>
+      <c r="I120" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K120" t="n">
+        <v>2044566087</v>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>LARCAS S.R.L.</t>
+        </is>
+      </c>
+      <c r="M120" t="n">
+        <v>30019587</v>
+      </c>
+      <c r="N120" s="3" t="n">
+        <v>46008</v>
+      </c>
+      <c r="O120" s="3" t="n">
+        <v>46008</v>
+      </c>
+      <c r="P120" t="inlineStr"/>
+      <c r="Q120" t="inlineStr"/>
+      <c r="R120" t="n">
+        <v>0</v>
+      </c>
+      <c r="S120" t="inlineStr"/>
+      <c r="T120" s="3" t="n">
+        <v>46008</v>
+      </c>
+      <c r="U120" s="3" t="n">
+        <v>46008</v>
+      </c>
+      <c r="V120" t="inlineStr"/>
+      <c r="W120" t="inlineStr"/>
+      <c r="X120" t="inlineStr"/>
+      <c r="Y120" t="n">
+        <v>6161.37</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>7414.68</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>SISTEMAS AUXILIARES</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>0</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>GP/90-225-SI</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>5016476</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>OTROS SERVICIOS INTERNOS</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>SERVICIO DE GRUA</t>
+        </is>
+      </c>
+      <c r="I121" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" s="3" t="n">
+        <v>45957</v>
+      </c>
+      <c r="O121" s="3" t="n">
+        <v>45957</v>
+      </c>
+      <c r="P121" t="inlineStr"/>
+      <c r="Q121" t="inlineStr"/>
+      <c r="R121" t="n">
+        <v>0</v>
+      </c>
+      <c r="S121" t="inlineStr"/>
+      <c r="T121" s="3" t="n">
+        <v>45957</v>
+      </c>
+      <c r="U121" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="V121" t="inlineStr"/>
+      <c r="W121" t="inlineStr"/>
+      <c r="X121" t="inlineStr"/>
+      <c r="Y121" t="inlineStr"/>
+      <c r="Z121" t="inlineStr"/>
+      <c r="AA121" t="inlineStr"/>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>CASCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>0</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>TASA 111 (DESGUACE)</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>GP/90</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>GP/90-225-SI</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>5016476</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>OTROS SERVICIOS INTERNOS</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>0020</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>LIMPIEZA DE PATIO</t>
+        </is>
+      </c>
+      <c r="I122" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>PEN</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" s="3" t="n">
+        <v>45985</v>
+      </c>
+      <c r="O122" s="3" t="n">
+        <v>45985</v>
+      </c>
+      <c r="P122" t="inlineStr"/>
+      <c r="Q122" t="inlineStr"/>
+      <c r="R122" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" t="inlineStr"/>
+      <c r="T122" s="3" t="n">
+        <v>45985</v>
+      </c>
+      <c r="U122" s="3" t="n">
+        <v>45985</v>
+      </c>
+      <c r="V122" t="inlineStr"/>
+      <c r="W122" t="inlineStr"/>
+      <c r="X122" t="inlineStr"/>
+      <c r="Y122" t="inlineStr"/>
+      <c r="Z122" t="inlineStr"/>
+      <c r="AA122" t="inlineStr"/>
+      <c r="AB122" t="inlineStr">
         <is>
           <t>CASCO</t>
         </is>
